--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_CO.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_CO.xlsx
@@ -2,27 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R14887873396a4fee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R9dfa86885aba4481"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="Rf55c351ab88249d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R5d290f3699104043"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="Ra9445f0c8c3a4739"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R409d3c15e44046b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R47edc39462334cf6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="Rfe4fc8e3f39f4b28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="Rabb5080de65a4249"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R6b97d633c00a4b4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R8ffded470f984514"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R99ac7d7f5b934966"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="Re9442e5cef224668"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Rea22a08b77994cc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R9429534875ce484f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R988068a1486c4199"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R3d88ebcb48554b41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R6f4556e6915f4a20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R1cf10d776f234a99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R11e7a546335f43b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R2165f257e37943b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="Rf8bd6be3fe2246f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Rbce874860282400f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R714b7b8db07e472e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R6a55b1ea921b40a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R4f13125598df46c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R300751f0c6644546"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R5585150dd7e646e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R2093a3cb76a04e60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="Reb188d061e17408c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="Rd4a62b6a6cd6481e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R67698dab8347469c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="Rf5fbaaaa00bd45ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="Rbe4b666c1abc445d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R2e37c8f1df4b4059"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="Rb6376b933f9a4120"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R95fd8b767bf64b19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R7325e571013a456d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="Rae828cb013914907"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R13d435639ac543fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R5a57e271ad9b4ae6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R723c3bf8deda473c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="Ra1a3c29b93804b5b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3057,6 +3058,41 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.5" customHeight="1">
+      <x:c r="A1" t="str">
+        <x:v>名前</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>ビアンカ・デル・コルボ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="19.5" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>出身地</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>カラスの島</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="19.5" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B3"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>

--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_CO.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_CO.xlsx
@@ -2,28 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="Rf8bd6be3fe2246f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Rbce874860282400f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R714b7b8db07e472e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R6a55b1ea921b40a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R4f13125598df46c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R300751f0c6644546"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R5585150dd7e646e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R2093a3cb76a04e60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="Reb188d061e17408c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="Rd4a62b6a6cd6481e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R67698dab8347469c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="Rf5fbaaaa00bd45ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="Rbe4b666c1abc445d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R2e37c8f1df4b4059"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="Rb6376b933f9a4120"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R95fd8b767bf64b19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R7325e571013a456d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="Rae828cb013914907"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R13d435639ac543fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R5a57e271ad9b4ae6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R723c3bf8deda473c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="Ra1a3c29b93804b5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R210f070c953b4b16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R9a9b7d6782774e09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R6f98b79abc6146ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="Rba5b3664993f4cea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R86897e56738b44da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="Reba58f16de5c43df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="Rf64476da609046f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="Re0ea849be7244360"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="Reb5ab109942a47ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="Reabc829f7d5b4572"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R8dcc42ae5d924783"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="Rd55340d05ce74e14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="Rc0298f2283504221"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R1f64240569264cbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R50b1c59404f243f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="Rda92c1e1225d4e46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="Raa404f2d21ee4dca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R2e2eaa906c7a41c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R5ec2c5d1fccb46bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R44ee0f343b734204"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R649d31b38eeb443d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="R43dac669b380423e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -559,7 +559,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -604,11 +604,11 @@
         <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"점프하여 세레나카를 아래로 크게 휘둘러 많은 적을 공격한다."</x:v>
       </x:c>
@@ -619,11 +619,11 @@
         <x:v>「ジャンプしてセレナカを下に大きく振り下ろし、多くの敵を攻撃します。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「ジャンプしてセレナカを下に大きく振り下ろし、多くの敵を攻撃します。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>ジャンプしてセレナカを大きく振り下ろし、多くの敵を攻撃する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -634,11 +634,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 6초</x:v>
       </x:c>
@@ -649,82 +649,118 @@
         <x:v>・再使用待機時間: 6秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 6秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：6秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1935.31%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ967.65%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 5 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 5 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大5ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大5ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大5打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Super Armor while using skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="8"/>
+      <x:c r="B11" s="6" t="str">
         <x:v>・점프 중 피해 감소 , 잡기 불가</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="6" t="str">
         <x:v>・While jumping Damage Reduction , Grab Immunity</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="6" t="str">
         <x:v>・ジャンプ中被害減少、免疫獲得</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ジャンプ中被害減少、免疫獲得</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" s="6" t="str">
+        <x:v>・ジャンプ中、ダメージ減少、キャッチ不可</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12"/>
+      <x:c r="B12" t="str">
         <x:v>・타격 성공 시 넉다운</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" t="str">
         <x:v>・Knockdown on hit</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" t="str">
         <x:v>・ヒット時ノックダウン</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・ヒット時ノックダウン</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="8" t="str"/>
-      <x:c r="B11" s="6" t="str">
+      <x:c r="E12" t="str">
+        <x:v>・打撃成功時、ノックダウン</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13"/>
+      <x:c r="B13" t="str">
         <x:v>・마지막 타격 지점에 회오리 지대 생성</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str">
+      <x:c r="C13" t="str">
         <x:v>・Create Whirlpool Zone at the last hit location</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="str">
+      <x:c r="D13" t="str">
         <x:v>・最後にヒットした位置にワールプールゾーンを作成</x:v>
       </x:c>
-      <x:c r="E11" s="6" t="str">
-        <x:v>・最後にヒットした位置にワールプールゾーンを作成</x:v>
+      <x:c r="E13" t="str">
+        <x:v>・最後の打撃地点に竜巻地帯作成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14" t="str">
+        <x:v>・竜巻地帯</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15" t="str">
+        <x:v>　打撃ダメージ1548.24%</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -744,7 +780,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -789,11 +825,11 @@
         <x:v>PvP ｜系列 鮮明 洗練された 洗練された</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvP ｜系列 鮮明 洗練された 洗練された</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"후방으로 뛰어올라 작살을 발사하며 그 반동으로 뒤로 이동한다."</x:v>
       </x:c>
@@ -804,11 +840,11 @@
         <x:v>「後ろに飛び上がって銛を発射し、その反動で後ろに進みます。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「後ろに飛び上がって銛を発射し、その反動で後ろに進みます。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>後方にジャンプしながら銛を発射し、反動でさらに移動する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -819,11 +855,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 8초</x:v>
       </x:c>
@@ -834,143 +870,155 @@
         <x:v>・再使用待機時間: 8秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 8秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：8秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ813.74%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ406.87%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 버튼 유지 시 최대 2 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 2 hits when holding skill button</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術ボタン押しっぱなしで最大2ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術ボタン押しっぱなしで最大2ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキルボタン長押しで最大2打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・즉시 발동 기술</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Instant Activation Skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・即時発動技術</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・即時発動技術</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・即時発動スキル</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="8"/>
+      <x:c r="B11" s="6" t="str">
         <x:v>・점프 중 슈퍼 아머 , 피해 감소 , 잡기 불가</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="6" t="str">
         <x:v>・While jumping Super Armor , Damage Reduction , Grab Immunity</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="6" t="str">
         <x:v>・ジャンプ中スーパーアーマー、被害減少、掴み無効</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ジャンプ中スーパーアーマー、被害減少、掴み無効</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" s="6" t="str">
+        <x:v>・ジャンプ中、スーパーアーマー、ダメージ減少、キャッチ不可</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="8"/>
+      <x:c r="B12" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" s="6" t="str">
         <x:v>・Super Armor while using skill</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" s="6" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="8" t="str"/>
-      <x:c r="B11" s="6" t="str">
+      <x:c r="E12" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="8"/>
+      <x:c r="B13" s="6" t="str">
         <x:v>・타격 성공 시 넉다운</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str">
+      <x:c r="C13" s="6" t="str">
         <x:v>・Knockdown on hit</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="str">
+      <x:c r="D13" s="6" t="str">
         <x:v>・ヒット時ノックダウン</x:v>
       </x:c>
-      <x:c r="E11" s="6" t="str">
-        <x:v>・ヒット時ノックダウン</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="8" t="str"/>
-      <x:c r="B12" s="6" t="str">
+      <x:c r="E13" s="6" t="str">
+        <x:v>・打撃成功時、ノックダウン</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="8"/>
+      <x:c r="B14" s="6" t="str">
         <x:v>・재장전</x:v>
       </x:c>
-      <x:c r="C12" s="6" t="str">
+      <x:c r="C14" s="6" t="str">
         <x:v>・Reload</x:v>
       </x:c>
-      <x:c r="D12" s="6" t="str">
+      <x:c r="D14" s="6" t="str">
         <x:v>・リロード</x:v>
       </x:c>
-      <x:c r="E12" s="6" t="str">
+      <x:c r="E14" s="6" t="str">
         <x:v>・リロード</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="30" customHeight="1">
-      <x:c r="A13" s="8" t="str"/>
-      <x:c r="B13" s="6" t="str">
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="8"/>
+      <x:c r="B15" s="6" t="str">
         <x:v>・1 타격 추가</x:v>
       </x:c>
-      <x:c r="C13" s="6" t="str">
+      <x:c r="C15" s="6" t="str">
         <x:v>・1 additional hit</x:v>
       </x:c>
-      <x:c r="D13" s="6" t="str">
+      <x:c r="D15" s="6" t="str">
         <x:v>・追加ヒット1回</x:v>
       </x:c>
-      <x:c r="E13" s="6" t="str">
-        <x:v>・追加ヒット1回</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="30" customHeight="1">
-      <x:c r="A14" s="8" t="str"/>
-      <x:c r="B14" s="6" t="str">
+      <x:c r="E15" s="6"/>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16"/>
+      <x:c r="B16" t="str">
         <x:v>・피해량 50% 적용</x:v>
       </x:c>
-      <x:c r="C14" s="6" t="str">
+      <x:c r="C16" t="str">
         <x:v>・Apply 50% damage</x:v>
       </x:c>
-      <x:c r="D14" s="6" t="str">
+      <x:c r="D16" t="str">
         <x:v>・50%のダメージを与える</x:v>
       </x:c>
-      <x:c r="E14" s="6" t="str">
-        <x:v>・50%のダメージを与える</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="30" customHeight="1">
-      <x:c r="A15" s="8" t="str"/>
-      <x:c r="B15" s="6" t="str">
+      <x:c r="E16"/>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17"/>
+      <x:c r="B17" t="str">
         <x:v>・공격 범위 증가</x:v>
       </x:c>
-      <x:c r="C15" s="6" t="str">
+      <x:c r="C17" t="str">
         <x:v>・Attack range increased</x:v>
       </x:c>
-      <x:c r="D15" s="6" t="str">
+      <x:c r="D17" t="str">
         <x:v>・攻撃範囲が増加しました</x:v>
       </x:c>
-      <x:c r="E15" s="6" t="str">
-        <x:v>・攻撃範囲が増加しました</x:v>
-      </x:c>
+      <x:c r="E17"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -989,7 +1037,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -1034,11 +1082,11 @@
         <x:v>PvP ｜系列 無欠 鮮明 洗練された</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvP ｜系列 無欠 鮮明 洗練された</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"밧줄을 적에게 던져 맞춘 후 밧줄을 타고 적에게 날아가 공격한다."</x:v>
       </x:c>
@@ -1049,11 +1097,11 @@
         <x:v>「敵に向かってロープを投げ、そのロープを使って敵に向かって飛んで攻撃する」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「敵に向かってロープを投げ、そのロープを使って敵に向かって飛んで攻撃する」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>ロープを敵に投げて狙いを定めた後、投げたロープを利用して敵の元へ飛んでいき攻撃する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 3</x:v>
       </x:c>
@@ -1064,11 +1112,11 @@
         <x:v>・最大使用回数: 3</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 5초</x:v>
       </x:c>
@@ -1079,67 +1127,85 @@
         <x:v>・再使用待機時間: 5秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 5秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：5秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1144.23%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ572.12%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 2 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 2 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大2ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大2ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大2打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Super Armor while using skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・첫 타격 성공 시 경직</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・On first hit success, Stiffness</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・初撃成功時、硬さ</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・初撃成功時、硬さ</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" t="str">
+        <x:v>・1回目の打撃成功時、硬直</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12"/>
+      <x:c r="B12" t="str">
         <x:v>・마지막 타격 성공 시 기절</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" t="str">
         <x:v>・On last hit success, Stun</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" t="str">
         <x:v>・最終ヒット成功時、スタン</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・最終ヒット成功時、スタン</x:v>
+      <x:c r="E12" t="str">
+        <x:v>・最後の打撃成功時、気絶</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1159,7 +1225,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -1204,11 +1270,11 @@
         <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"파트라카에 작살을 장전하여 발사한 후 빠르게 재장전하여 다시 발사한다."</x:v>
       </x:c>
@@ -1219,11 +1285,11 @@
         <x:v>「パトラカに銛を装填して発射し、すぐに再装填して再度発射します。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「パトラカに銛を装填して発射し、すぐに再装填して再度発射します。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>パトラカに銛を装填して発射した後、素早く再装填し続けて発射する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 2</x:v>
       </x:c>
@@ -1234,11 +1300,11 @@
         <x:v>・最大使用回数: 2</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 6초</x:v>
       </x:c>
@@ -1249,97 +1315,115 @@
         <x:v>・再使用待機時間: 6秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 6秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：6秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ2420.54%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ1210.27%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 버튼 유지 시 최대 3 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 3 hits when holding skill button</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術ボタン押しっぱなしで最大3ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術ボタン押しっぱなしで最大3ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキルボタン長押しで最大3打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Super Armor while using skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="8"/>
+      <x:c r="B11" s="6" t="str">
         <x:v>・타격 성공 시 넉다운</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="6" t="str">
         <x:v>・Knockdown on hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="6" t="str">
         <x:v>・ヒット時ノックダウン</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット時ノックダウン</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" s="6" t="str">
+        <x:v>・打撃成功時、ノックダウン</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="8"/>
+      <x:c r="B12" s="6" t="str">
         <x:v>・타격 성공 시 정신력 회복 10</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" s="6" t="str">
         <x:v>・MP recovery 10 on hit</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" s="6" t="str">
         <x:v>・ヒット時精神力回復10</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・ヒット時精神力回復10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="8" t="str"/>
-      <x:c r="B11" s="6" t="str">
+      <x:c r="E12" s="6" t="str">
+        <x:v>・打撃成功時、MP10回復</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13"/>
+      <x:c r="B13" t="str">
         <x:v>・재장전</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str">
+      <x:c r="C13" t="str">
         <x:v>・Reload</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="str">
+      <x:c r="D13" t="str">
         <x:v>・リロード</x:v>
       </x:c>
-      <x:c r="E11" s="6" t="str">
+      <x:c r="E13" t="str">
         <x:v>・リロード</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="8" t="str"/>
-      <x:c r="B12" s="6" t="str">
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14"/>
+      <x:c r="B14" t="str">
         <x:v>・1타격 추가</x:v>
       </x:c>
-      <x:c r="C12" s="6" t="str">
+      <x:c r="C14" t="str">
         <x:v>・1 additional hit</x:v>
       </x:c>
-      <x:c r="D12" s="6" t="str">
+      <x:c r="D14" t="str">
         <x:v>・追加ヒット1回</x:v>
       </x:c>
-      <x:c r="E12" s="6" t="str">
-        <x:v>・追加ヒット1回</x:v>
+      <x:c r="E14" t="str">
+        <x:v>　1打撃追加</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1359,7 +1443,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -1404,11 +1488,11 @@
         <x:v>PvP ｜系列 鮮明 洗練された かすかな</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvP ｜系列 鮮明 洗練された かすかな</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"적 대상을 따라가는 파도를 일으켜 대상의 위치에서 파도가 솟아오르게하여 공격한다."</x:v>
       </x:c>
@@ -1419,11 +1503,11 @@
         <x:v>「敵のターゲットを追跡する波を作成し、ターゲットの位置で押し寄せます。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「敵のターゲットを追跡する波を作成し、ターゲットの位置で押し寄せます。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>対象の敵を追う波を起こし、敵の足元から波を湧き上がらせて攻撃する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -1434,11 +1518,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 7초</x:v>
       </x:c>
@@ -1449,52 +1533,106 @@
         <x:v>・再使用待機時間: 7秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 7秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：7秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1652.78%x3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ826.39%x3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Super Armor while using skill</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10"/>
+      <x:c r="B10" t="str">
         <x:v>・타격 성공 시 띄우기</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" t="str">
         <x:v>・Knock-up on hit</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" t="str">
         <x:v>・ヒット時浮かせ</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・ヒット時浮かせ</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" t="str">
+        <x:v>・打撃成功時、浮かす</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・타격 지점에 회오리 지대 생성</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・Create Whirlpool Zone at hit location</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・ヒットした場所に渦巻きゾーンを作成</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒットした場所に渦巻きゾーンを作成</x:v>
+      <x:c r="E11" t="str">
+        <x:v>・打撃地点に竜巻地帯作成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12"/>
+      <x:c r="B12"/>
+      <x:c r="C12"/>
+      <x:c r="D12"/>
+      <x:c r="E12" t="str">
+        <x:v>・竜巻地帯</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13" t="str">
+        <x:v>　打撃ダメージ1322.22%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14" t="str">
+        <x:v>　PVP打撃ダメージ123.96%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15" t="str">
+        <x:v>　最大5打撃</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1514,7 +1652,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -1559,11 +1697,11 @@
         <x:v>PvE PvP ｜系列 無欠 鮮明 かすかな</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 無欠 鮮明 かすかな</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"집중하여 적의 위치를 파악한 후 작살을 발사한다."</x:v>
       </x:c>
@@ -1574,11 +1712,11 @@
         <x:v>「敵の位置を特定し、銛を発射することに集中してください。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「敵の位置を特定し、銛を発射することに集中してください。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>集中して敵に狙いを定めた後、銛を発射する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -1589,11 +1727,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 7초</x:v>
       </x:c>
@@ -1604,112 +1742,130 @@
         <x:v>・再使用待機時間: 7秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 7秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：7秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ2103.02%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ1051.51%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Super Armor while using skill</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・타격 성공 시 띄우기</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Knock-up on hit</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・ヒット時浮かせ</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・ヒット時浮かせ</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・打撃成功時、浮かす</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="8"/>
+      <x:c r="B11" s="6" t="str">
         <x:v>・기술 버튼 유지 시 기술 피해량 30% 증가</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="6" t="str">
         <x:v>・Skill damage 30% increase when holding skill button</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="6" t="str">
         <x:v>・技術ボタン長押しで技術被害量30%増加</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・技術ボタン長押しで技術被害量30%増加</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" s="6" t="str">
+        <x:v>・スキルボタン長押しでスキルダメージ量30%増加</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="8"/>
+      <x:c r="B12" s="6" t="str">
         <x:v>・재장전</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" s="6" t="str">
         <x:v>・Reload</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" s="6" t="str">
         <x:v>・リロード</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
+      <x:c r="E12" s="6" t="str">
         <x:v>・リロード</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="8" t="str"/>
-      <x:c r="B11" s="6" t="str">
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="8"/>
+      <x:c r="B13" s="6" t="str">
         <x:v>・1 타격 추가</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str">
+      <x:c r="C13" s="6" t="str">
         <x:v>・1 additional hit</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="str">
+      <x:c r="D13" s="6" t="str">
         <x:v>・追加ヒット1回</x:v>
       </x:c>
-      <x:c r="E11" s="6" t="str">
-        <x:v>・追加ヒット1回</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="8" t="str"/>
-      <x:c r="B12" s="6" t="str">
+      <x:c r="E13" s="6" t="str">
+        <x:v>　1打撃追加</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14"/>
+      <x:c r="B14" t="str">
         <x:v>・피해량 50% 적용</x:v>
       </x:c>
-      <x:c r="C12" s="6" t="str">
+      <x:c r="C14" t="str">
         <x:v>・Apply 50% damage</x:v>
       </x:c>
-      <x:c r="D12" s="6" t="str">
+      <x:c r="D14" t="str">
         <x:v>・50%のダメージを与える</x:v>
       </x:c>
-      <x:c r="E12" s="6" t="str">
-        <x:v>・50%のダメージを与える</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="30" customHeight="1">
-      <x:c r="A13" s="8" t="str"/>
-      <x:c r="B13" s="6" t="str">
+      <x:c r="E14" t="str">
+        <x:v>　打撃ダメージ50%適用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15"/>
+      <x:c r="B15" t="str">
         <x:v>・공격 범위 및 공격 속도 증가</x:v>
       </x:c>
-      <x:c r="C13" s="6" t="str">
+      <x:c r="C15" t="str">
         <x:v>・Attack range and Attack Speed increased</x:v>
       </x:c>
-      <x:c r="D13" s="6" t="str">
+      <x:c r="D15" t="str">
         <x:v>・攻撃範囲と攻撃速度が増加しました</x:v>
       </x:c>
-      <x:c r="E13" s="6" t="str">
-        <x:v>・攻撃範囲と攻撃速度が増加しました</x:v>
+      <x:c r="E15" t="str">
+        <x:v>　攻撃範囲、攻撃速度増加</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1729,7 +1885,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -1774,11 +1930,11 @@
         <x:v>「艦長として戦場を秩序正しく掌握せよ」</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>「艦長として戦場を秩序正しく掌握せよ」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>船長として指揮し、戦場を一糸乱れず統制する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -1789,11 +1945,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・재사용 대기시간 : 90초</x:v>
       </x:c>
@@ -1804,11 +1960,11 @@
         <x:v>・再使用待機時間: 90秒</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・再使用待機時間: 90秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>再使用待機時間：93秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・10초 간 2초 마다 생명력 회복 115~400</x:v>
       </x:c>
@@ -1819,11 +1975,11 @@
         <x:v>・10秒間、2秒ごとに生命力 115~400回復</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・10秒間、2秒ごとに生命力 115~400回復</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
+        <x:v>・10秒間、2秒ごとにHP250回復</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
       <x:c r="B7" s="6" t="str">
         <x:v>・30초 간 공격력 +43~100</x:v>
       </x:c>
@@ -1834,11 +1990,11 @@
         <x:v>・30秒間AP +43~100</x:v>
       </x:c>
       <x:c r="E7" s="6" t="str">
-        <x:v>・30秒間AP +43~100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
+        <x:v>・30秒間、攻撃力+70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
       <x:c r="B8" s="6" t="str">
         <x:v>・30초 간 방어력 +43~100</x:v>
       </x:c>
@@ -1849,11 +2005,11 @@
         <x:v>・30秒間DP+43~100</x:v>
       </x:c>
       <x:c r="E8" s="6" t="str">
-        <x:v>・30秒間DP+43~100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
+        <x:v>・30秒間、防御力+70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
       <x:c r="B9" s="6" t="str">
         <x:v>・30초 간 치명타 피해량 +50%</x:v>
       </x:c>
@@ -1864,11 +2020,11 @@
         <x:v>・30秒間致命打被害量+50%</x:v>
       </x:c>
       <x:c r="E9" s="6" t="str">
-        <x:v>・30秒間致命打被害量+50%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
+        <x:v>・30秒間、クリティカルダメージ量+50%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
       <x:c r="B10" s="6" t="str">
         <x:v>・30초 간 흑정령 기술 피해량 +20%</x:v>
       </x:c>
@@ -1879,11 +2035,11 @@
         <x:v>・闇の精霊の怒り技術被害量+20% (30秒間)</x:v>
       </x:c>
       <x:c r="E10" s="6" t="str">
-        <x:v>・闇の精霊の怒り技術被害量+20% (30秒間)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="8" t="str"/>
+        <x:v>・30秒間、闇の精霊スキルダメージ量+20%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A11" s="8"/>
       <x:c r="B11" s="6" t="str">
         <x:v>・기술 사용 시 30초 간 회피 기술 재사용 시간 2초 감소</x:v>
       </x:c>
@@ -1894,7 +2050,7 @@
         <x:v>・技術使用時、30秒間回避技術の再使用待機時間が2秒減少する</x:v>
       </x:c>
       <x:c r="E11" s="6" t="str">
-        <x:v>・技術使用時、30秒間回避技術の再使用待機時間が2秒減少する</x:v>
+        <x:v>・スキル使用時30秒間、回避スキル再使用時間2秒減少</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2054,7 +2210,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -2099,11 +2255,11 @@
         <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"태양을 향해 로프를 던져 잠시동안 공중에 체공하며 작살을 발사한다."</x:v>
       </x:c>
@@ -2114,11 +2270,11 @@
         <x:v>「太陽に向かってロープを投げて、一瞬空中に浮かび、銛を発射します。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「太陽に向かってロープを投げて、一瞬空中に浮かび、銛を発射します。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>太陽に向かってロープを投げ、しばらく滞空しながら銛を放つ。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -2129,11 +2285,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 15초</x:v>
       </x:c>
@@ -2144,97 +2300,115 @@
         <x:v>・再使用待機時間: 15秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 15秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：15秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ3466.1%x3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ1733.05%x3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Super Armor while using skill</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・점프 중 잡기 불가</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・While jumping Grab Immunity</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・ジャンプ中に免疫を獲得する</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・ジャンプ中に免疫を獲得する</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・ジャンプ中、キャッチ不可</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="8"/>
+      <x:c r="B11" s="6" t="str">
         <x:v>・타격 성공 시 넉백</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="6" t="str">
         <x:v>・Knockback on hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="6" t="str">
         <x:v>・ヒット時ノックバック</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット時ノックバック</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" s="6" t="str">
+        <x:v>・打撃成功時、ノックバック</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="8"/>
+      <x:c r="B12" s="6" t="str">
         <x:v>・재장전</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" s="6" t="str">
         <x:v>・Reload</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" s="6" t="str">
         <x:v>・リロード</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
+      <x:c r="E12" s="6" t="str">
         <x:v>・リロード</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="8" t="str"/>
-      <x:c r="B11" s="6" t="str">
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13"/>
+      <x:c r="B13" t="str">
         <x:v>・2 타격 추가</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str">
+      <x:c r="C13" t="str">
         <x:v>・2 additional hits</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="str">
+      <x:c r="D13" t="str">
         <x:v>・追加ヒット2本</x:v>
       </x:c>
-      <x:c r="E11" s="6" t="str">
-        <x:v>・追加ヒット2本</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="8" t="str"/>
-      <x:c r="B12" s="6" t="str">
+      <x:c r="E13" t="str">
+        <x:v>　2打撃追加</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14"/>
+      <x:c r="B14" t="str">
         <x:v>・피해량 33% 적용</x:v>
       </x:c>
-      <x:c r="C12" s="6" t="str">
+      <x:c r="C14" t="str">
         <x:v>・Apply 33% damage</x:v>
       </x:c>
-      <x:c r="D12" s="6" t="str">
+      <x:c r="D14" t="str">
         <x:v>・33%のダメージを与える</x:v>
       </x:c>
-      <x:c r="E12" s="6" t="str">
-        <x:v>・33%のダメージを与える</x:v>
+      <x:c r="E14" t="str">
+        <x:v>　打撃ダメージ33%適用</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2254,7 +2428,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -2299,11 +2473,11 @@
         <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"인어의 형상으로 거대한 낭만 고래를 소환한 뒤 전방을 덮치게 한다."</x:v>
       </x:c>
@@ -2314,11 +2488,11 @@
         <x:v>「巨大なロマンティッククジラを人魚の姿で召喚し、前方に攻撃します。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「巨大なロマンティッククジラを人魚の姿で召喚し、前方に攻撃します。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>人魚の姿で巨大なロマンクジラを召喚し、前方を襲撃させる。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -2329,11 +2503,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 16초</x:v>
       </x:c>
@@ -2344,52 +2518,70 @@
         <x:v>・再使用待機時間: 16秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 16秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：16秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ2074.6%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ1037.3%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 6 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 6 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大6ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大6ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大6打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10"/>
+      <x:c r="B10" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" t="str">
         <x:v>・Super Armor while using skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・타격 성공 시 기절</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・Stun on hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・ヒット時に気絶させる</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット時に気絶させる</x:v>
+      <x:c r="E11" t="str">
+        <x:v>・打撃成功時、気絶</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2775,7 +2967,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -2820,11 +3012,11 @@
         <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"근거리에서 파트라카를 내려 베어 적의 자세를 무너뜨리고 제압한다."</x:v>
       </x:c>
@@ -2835,11 +3027,11 @@
         <x:v>「至近距離からパトラカを打ち下ろし、敵の体勢を崩して制圧する。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「至近距離からパトラカを打ち下ろし、敵の体勢を崩して制圧する。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>近距離でパトラカを振り下ろし、敵の体勢を崩して制圧する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -2850,11 +3042,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 15초</x:v>
       </x:c>
@@ -2865,67 +3057,85 @@
         <x:v>・再使用待機時間: 15秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 15秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：15秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ2617.4%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ1308.7%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 2 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 2 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大2ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大2ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大2打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Super Armor while using skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・타격 성공 시 띄우기</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・On hit success, Knock-up</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・ヒット成功時、浮かせ</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット成功時、浮かせ</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" t="str">
+        <x:v>・打撃成功時、浮かす</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12"/>
+      <x:c r="B12" t="str">
         <x:v>・마지막 타격 성공 시 바운드</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" t="str">
         <x:v>・On last hit success, Bound</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" t="str">
         <x:v>・最後のヒット成功時、バウンド</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・最後のヒット成功時、バウンド</x:v>
+      <x:c r="E12" t="str">
+        <x:v>・最後の打撃成功時、バウンド</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3200,7 +3410,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -3245,11 +3455,11 @@
         <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"세레나카를 크게 휘둘러 파도를 일으켜 먼 거리에 있는 적을 공격한다."</x:v>
       </x:c>
@@ -3260,11 +3470,11 @@
         <x:v>「セレナカを大きく振って波を起こし、遠くの敵を攻撃する」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「セレナカを大きく振って波を起こし、遠くの敵を攻撃する」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>セレナカを大きく振り回して波を巻き起こし、遠くにいる敵を攻撃する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 2</x:v>
       </x:c>
@@ -3275,11 +3485,11 @@
         <x:v>・最大使用回数: 2</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 6초</x:v>
       </x:c>
@@ -3290,67 +3500,85 @@
         <x:v>・再使用待機時間: 6秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 6秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：6秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1358.95%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ679.48%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 버튼 유지 시 최대 2 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 2 hits when holding skill button</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術ボタン押しっぱなしで最大2ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術ボタン押しっぱなしで最大2ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキルボタン長押しで最大2打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・기술 사용 중 전방 가드</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Forward Guard while using skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・技術使用中の前衛ガード</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用中の前衛ガード</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・スキル使用中、前方ガード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・타격 성공 시 넉백</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・Knockback on hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・ヒット時ノックバック</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット時ノックバック</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" t="str">
+        <x:v>・打撃成功時、ノックバック</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12"/>
+      <x:c r="B12" t="str">
         <x:v>・마지막 타격 성공 시 넉다운</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" t="str">
         <x:v>・Knockdown on last hit</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" t="str">
         <x:v>・最後のヒットでノックダウン</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・最後のヒットでノックダウン</x:v>
+      <x:c r="E12" t="str">
+        <x:v>・最後の打撃成功時、ノックダウン</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3370,7 +3598,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -3415,11 +3643,11 @@
         <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"발사했던 작살을 회수하며 작살을 발사해 공격한다."</x:v>
       </x:c>
@@ -3430,11 +3658,11 @@
         <x:v>「前に発射した銛を回収しながら銛を発射します。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「前に発射した銛を回収しながら銛を発射します。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>銛を装填した後、敵に向けて発射し攻撃する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 2</x:v>
       </x:c>
@@ -3445,11 +3673,11 @@
         <x:v>・最大使用回数: 2</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 7초</x:v>
       </x:c>
@@ -3460,112 +3688,130 @@
         <x:v>・再使用待機時間: 7秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 7秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：7秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ2039.52%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ1019.76%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 2타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 2 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大2ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大2ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大2打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・기술 사용 중 전방 가드</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Forward Guard while using skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・技術使用中の前衛ガード</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用中の前衛ガード</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・スキル使用中、前方ガード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="8"/>
+      <x:c r="B11" s="6" t="str">
         <x:v>・타격 성공 시 넉백</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="6" t="str">
         <x:v>・Knockback on hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="6" t="str">
         <x:v>・ヒット時ノックバック</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット時ノックバック</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" s="6" t="str">
+        <x:v>・打撃成功時、ノックバック</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="8"/>
+      <x:c r="B12" s="6" t="str">
         <x:v>・타격 성공 시 정신력 회복 10</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" s="6" t="str">
         <x:v>・MP recovery 10 on hit</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" s="6" t="str">
         <x:v>・ヒット時精神力回復10</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・ヒット時精神力回復10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="8" t="str"/>
-      <x:c r="B11" s="6" t="str">
+      <x:c r="E12" s="6" t="str">
+        <x:v>・打撃成功時、MP10回復</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="8"/>
+      <x:c r="B13" s="6" t="str">
         <x:v>・재장전</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str">
+      <x:c r="C13" s="6" t="str">
         <x:v>・Reload</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="str">
+      <x:c r="D13" s="6" t="str">
         <x:v>・リロード</x:v>
       </x:c>
-      <x:c r="E11" s="6" t="str">
+      <x:c r="E13" s="6" t="str">
         <x:v>・リロード</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="8" t="str"/>
-      <x:c r="B12" s="6" t="str">
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14"/>
+      <x:c r="B14" t="str">
         <x:v>・1 타격 추가</x:v>
       </x:c>
-      <x:c r="C12" s="6" t="str">
+      <x:c r="C14" t="str">
         <x:v>・1 additional hit</x:v>
       </x:c>
-      <x:c r="D12" s="6" t="str">
+      <x:c r="D14" t="str">
         <x:v>・追加ヒット1回</x:v>
       </x:c>
-      <x:c r="E12" s="6" t="str">
-        <x:v>・追加ヒット1回</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="30" customHeight="1">
-      <x:c r="A13" s="8" t="str"/>
-      <x:c r="B13" s="6" t="str">
+      <x:c r="E14" t="str">
+        <x:v>　1打撃追加</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15"/>
+      <x:c r="B15" t="str">
         <x:v>・공격 범위 증가</x:v>
       </x:c>
-      <x:c r="C13" s="6" t="str">
+      <x:c r="C15" t="str">
         <x:v>・Attack range increased</x:v>
       </x:c>
-      <x:c r="D13" s="6" t="str">
+      <x:c r="D15" t="str">
         <x:v>・攻撃範囲が増加しました</x:v>
       </x:c>
-      <x:c r="E13" s="6" t="str">
-        <x:v>・攻撃範囲が増加しました</x:v>
+      <x:c r="E15" t="str">
+        <x:v>　攻撃範囲増加</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3585,7 +3831,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -3630,11 +3876,11 @@
         <x:v>PvE ｜系列 無欠 鮮明 洗練された</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE ｜系列 無欠 鮮明 洗練された</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"세레나카를 강하게 휘둘러 주변의 적을 베어낸다."</x:v>
       </x:c>
@@ -3645,11 +3891,11 @@
         <x:v>「セレナカを強く振って周囲の敵を斬り裂く」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「セレナカを強く振って周囲の敵を斬り裂く」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>セレナカを強く振り回し、周辺の敵を斬る。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 2</x:v>
       </x:c>
@@ -3660,11 +3906,11 @@
         <x:v>・最大使用回数: 2</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 5초</x:v>
       </x:c>
@@ -3675,52 +3921,70 @@
         <x:v>・再使用待機時間: 5秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 5秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：5秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1433.82%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ716.91%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 2 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 2 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大2ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大2ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大2打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10"/>
+      <x:c r="B10" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" t="str">
         <x:v>・Super Armor while using skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・타격 성공 시 기절</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・Stun on hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・ヒット時に気絶させる</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット時に気絶させる</x:v>
+      <x:c r="E11" t="str">
+        <x:v>・打撃成功時、気絶</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3740,7 +4004,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -3785,11 +4049,11 @@
         <x:v>PvE PvP ｜系列 無欠 鮮明 かすかな</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 無欠 鮮明 かすかな</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"공중으로 힘차게 작살을 쏘아올려 선장의 명령을 내린다. 팔딱생선해적단의 배에서 거대한 닻을 떨어뜨린다."</x:v>
       </x:c>
@@ -3800,11 +4064,11 @@
         <x:v>「船長の命令を出すために銛を空に向かって勢いよく発射してください。飛び魚海賊団の船から巨大な錨を落としてください。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「船長の命令を出すために銛を空に向かって勢いよく発射してください。飛び魚海賊団の船から巨大な錨を落としてください。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>空中に銛を放って船長の命令を下し、パタパタ海賊団が船から巨大なアンカーを放つ。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -3815,11 +4079,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 8초</x:v>
       </x:c>
@@ -3830,52 +4094,70 @@
         <x:v>・再使用待機時間: 8秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 8秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：8秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1856.39%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ928.2%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 버튼 유지 시 최대 2 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 2 hits when holding skill button</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術ボタン押しっぱなしで最大2ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術ボタン押しっぱなしで最大2ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキルボタン長押しで最大2打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10"/>
+      <x:c r="B10" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" t="str">
         <x:v>・Super Armor while using skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・타격 성공 시 바운드</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・Bound on hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・ヒット時にバウンド</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット時にバウンド</x:v>
+      <x:c r="E11" t="str">
+        <x:v>・打撃成功時、バウンド</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3895,7 +4177,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -3940,11 +4222,11 @@
         <x:v>PvP ｜系列 燦爛 鮮明 洗練された</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvP ｜系列 燦爛 鮮明 洗練された</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"잠수하여 적의 위치로 헤엄쳐 이동한 후 순식간에 솟구치며 공격한다."</x:v>
       </x:c>
@@ -3955,11 +4237,11 @@
         <x:v>「潜水して泳いで敵のいる場所まで到達し、その後急上昇して攻撃します。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「潜水して泳いで敵のいる場所まで到達し、その後急上昇して攻撃します。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>潜水して敵の位置まで泳いで移動した後、瞬時に跳ね上がり攻撃する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -3970,11 +4252,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 11초</x:v>
       </x:c>
@@ -3985,52 +4267,70 @@
         <x:v>・再使用待機時間: 11秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 11秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：11秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ772.63%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ459.72%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 2 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 2 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大2ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大2ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大2打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10"/>
+      <x:c r="B10" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" t="str">
         <x:v>・Super Armor while using skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・타격 성공 시 기절</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・Stun on hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・ヒット時に気絶させる</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット時に気絶させる</x:v>
+      <x:c r="E11" t="str">
+        <x:v>・打撃成功時、気絶</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4050,7 +4350,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -4095,11 +4395,11 @@
         <x:v>PvP ｜系列 無欠 鮮明 かすかな</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvP ｜系列 無欠 鮮明 かすかな</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"미끄러지듯 이동하며 작살을 적에게 발사한다."</x:v>
       </x:c>
@@ -4110,11 +4410,11 @@
         <x:v>「スライドして敵に銛を発射します。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「スライドして敵に銛を発射します。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>滑るように移動し、銛を敵に発射する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 4</x:v>
       </x:c>
@@ -4125,11 +4425,11 @@
         <x:v>・最大使用回数: 4</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 4초</x:v>
       </x:c>
@@ -4140,97 +4440,115 @@
         <x:v>・再使用待機時間: 4秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 4秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：4秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1698.37%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ849.18%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Super Armor while using skill</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・타격 성공 시 기절</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Stun on hit</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・ヒット時に気絶させる</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・ヒット時に気絶させる</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・打撃成功時、気絶</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="8"/>
+      <x:c r="B11" s="6" t="str">
         <x:v>・이동 공격 가능</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="6" t="str">
         <x:v>・Mobile attack available</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="6" t="str">
         <x:v>・モバイル攻撃が可能</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・モバイル攻撃が可能</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" s="6" t="str">
+        <x:v>・移動攻撃可能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="8"/>
+      <x:c r="B12" s="6" t="str">
         <x:v>・재장전</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" s="6" t="str">
         <x:v>・Reload</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" s="6" t="str">
         <x:v>・リロード</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
+      <x:c r="E12" s="6" t="str">
         <x:v>・リロード</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="8" t="str"/>
-      <x:c r="B11" s="6" t="str">
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13"/>
+      <x:c r="B13" t="str">
         <x:v>・1 타격 추가</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str">
+      <x:c r="C13" t="str">
         <x:v>・1 additional hit</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="str">
+      <x:c r="D13" t="str">
         <x:v>・追加ヒット1回</x:v>
       </x:c>
-      <x:c r="E11" s="6" t="str">
-        <x:v>・追加ヒット1回</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="8" t="str"/>
-      <x:c r="B12" s="6" t="str">
+      <x:c r="E13" t="str">
+        <x:v>　1打撃追加</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14"/>
+      <x:c r="B14" t="str">
         <x:v>・공격 범위 증가</x:v>
       </x:c>
-      <x:c r="C12" s="6" t="str">
+      <x:c r="C14" t="str">
         <x:v>・Attack range increased</x:v>
       </x:c>
-      <x:c r="D12" s="6" t="str">
+      <x:c r="D14" t="str">
         <x:v>・攻撃範囲が増加しました</x:v>
       </x:c>
-      <x:c r="E12" s="6" t="str">
-        <x:v>・攻撃範囲が増加しました</x:v>
+      <x:c r="E14" t="str">
+        <x:v>　攻撃範囲増加</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
